--- a/week6/logboek.xlsx
+++ b/week6/logboek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xande\School\DEAI_Portfolio\week6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322A1858-943C-4E64-910F-902DAF6F44C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08BFA24-36B0-4279-9C40-62495DC913BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>hyperparameter</t>
   </si>
@@ -130,13 +130,103 @@
   </si>
   <si>
     <t>r2:0.8098</t>
+  </si>
+  <si>
+    <t>Epochs (max_iter): 1000 | Learning Rate (eta0): 0.001</t>
+  </si>
+  <si>
+    <t>MAE: $22,788.16</t>
+  </si>
+  <si>
+    <t>R-kwadraat (R2): 0.8370</t>
+  </si>
+  <si>
+    <t>RUN 2: SGD Experiment (Meer epochs, kleinere stapjes) ------ RUN 2: SGD Experiment (Meer epochs, kleinere stapjes)</t>
+  </si>
+  <si>
+    <t>Epochs (max_iter): 5000 | Learning Rate (eta0): 0.0001</t>
+  </si>
+  <si>
+    <t>MAE: $22,560.53</t>
+  </si>
+  <si>
+    <t>R-kwadraat (R2): 0.8319</t>
+  </si>
+  <si>
+    <t>RUN 1: SGD Baseline</t>
+  </si>
+  <si>
+    <t>overall qual</t>
+  </si>
+  <si>
+    <t>gr liv area</t>
+  </si>
+  <si>
+    <t>top 3 target saleprice:</t>
+  </si>
+  <si>
+    <t>neighborhood</t>
+  </si>
+  <si>
+    <t>max_iter</t>
+  </si>
+  <si>
+    <t>eta0</t>
+  </si>
+  <si>
+    <t>nu learning_rate='adaptive'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> learning_rate</t>
+  </si>
+  <si>
+    <t>SGDRegressor (learning rate constant):</t>
+  </si>
+  <si>
+    <t>RUN 3: SGD Baseline adaptive</t>
+  </si>
+  <si>
+    <t>MAE: $22,555.58</t>
+  </si>
+  <si>
+    <t>R-kwadraat (R2): 0.8320</t>
+  </si>
+  <si>
+    <t>Overall Qual', 'Gr Liv Area', 'Year Built', 'Total Bsmt SF'</t>
+  </si>
+  <si>
+    <t>nieuwe features:</t>
+  </si>
+  <si>
+    <t>Resultaten Experiment A (Alleen nieuwe features)</t>
+  </si>
+  <si>
+    <t>MAE: $22,532.72</t>
+  </si>
+  <si>
+    <t>nieuwe hyperparameters:</t>
+  </si>
+  <si>
+    <t>RUN 4: SGD Experiment</t>
+  </si>
+  <si>
+    <t>fit_intercept(), max_iter, tol</t>
+  </si>
+  <si>
+    <t>Epochs (max_iter): 1000 | Tolerance (tol): 0.001</t>
+  </si>
+  <si>
+    <t>MAE: $22,844.10</t>
+  </si>
+  <si>
+    <t>R-kwadraat (R2): 0.8260</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +270,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -201,12 +297,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,42 +596,184 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6922F587-9C52-450E-8AA3-3224E271934D}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
